--- a/DevKit_回归测试报告_第二轮.xlsx
+++ b/DevKit_回归测试报告_第二轮.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="381">
   <si>
     <t>DevKit 第二轮回归测试 · 结论汇总</t>
   </si>
@@ -272,6 +272,9 @@
     <t>根因定位</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>BUG-001</t>
   </si>
   <si>
@@ -338,6 +341,9 @@
     <t>计划开发（串口）</t>
   </si>
   <si>
+    <t>非Bug</t>
+  </si>
+  <si>
     <t>BUG-006</t>
   </si>
   <si>
@@ -530,6 +536,9 @@
     <t>待修</t>
   </si>
   <si>
+    <t>无并发情况，此Bug可关闭</t>
+  </si>
+  <si>
     <t>BUG-022</t>
   </si>
   <si>
@@ -548,6 +557,9 @@
     <t>0b8af71 反而把「WSDataFrame 是一次性对象，发送结束后要及时释放」的注释删除了，代码本身仍无 Dispose。长时间高频发送会累积底层缓冲。</t>
   </si>
   <si>
+    <t>依靠GC自动回收</t>
+  </si>
+  <si>
     <t>BUG-024</t>
   </si>
   <si>
@@ -578,6 +590,9 @@
     <t>已修复，建议收敛弹窗次数</t>
   </si>
   <si>
+    <t>回退到控制台输出，非Bug，属于用户体验</t>
+  </si>
+  <si>
     <t>NEW-01</t>
   </si>
   <si>
@@ -612,6 +627,9 @@
   </si>
   <si>
     <t>待修（轻微，可选）</t>
+  </si>
+  <si>
+    <t>非Bug，属于用户体验</t>
   </si>
   <si>
     <t>NEW-04</t>
@@ -660,6 +678,9 @@
   </si>
   <si>
     <t>TcpClientViewModel.cs:395-398、WsClientViewModel.cs:337-340、UdpClientViewModel.cs:265-268 的 throw 仅有 SendLoopInputAsync 与脚本路径两个 catch 能接住；SendMessageCommand 由 XAML 直接绑定，无对应 catch</t>
+  </si>
+  <si>
+    <t>代码回退，直接弹框提示，非Bug</t>
   </si>
   <si>
     <t>NEW-07</t>
@@ -2879,7 +2900,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2893,12 +2914,12 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:9">
+    <row r="3" ht="24" customHeight="1" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>69</v>
       </c>
@@ -2926,28 +2947,31 @@
       <c r="I3" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J3" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>14</v>
@@ -2956,56 +2980,56 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="76" hidden="1" customHeight="1" spans="1:9">
+    <row r="5" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="76" hidden="1" customHeight="1" spans="1:10">
+      <c r="A6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="76" hidden="1" customHeight="1" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>14</v>
@@ -3014,27 +3038,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="76" hidden="1" customHeight="1" spans="1:9">
+    <row r="7" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A7" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -3043,27 +3067,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="76" customHeight="1" spans="1:9">
+    <row r="8" ht="76" customHeight="1" spans="1:10">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>14</v>
@@ -3071,28 +3095,31 @@
       <c r="I8" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J8" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A9" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
@@ -3100,28 +3127,29 @@
       <c r="I9" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>14</v>
@@ -3129,57 +3157,59 @@
       <c r="I10" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" ht="76" hidden="1" customHeight="1" spans="1:10">
+      <c r="A12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="76" hidden="1" customHeight="1" spans="1:9">
-      <c r="A12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="C12" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>14</v>
@@ -3187,28 +3217,29 @@
       <c r="I12" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A13" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
@@ -3216,28 +3247,29 @@
       <c r="I13" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>14</v>
@@ -3245,28 +3277,29 @@
       <c r="I14" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A15" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
@@ -3274,28 +3307,29 @@
       <c r="I15" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A16" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>14</v>
@@ -3303,57 +3337,59 @@
       <c r="I16" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" ht="76" hidden="1" customHeight="1" spans="1:10">
+      <c r="A18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" ht="76" hidden="1" customHeight="1" spans="1:9">
-      <c r="A18" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="C18" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>14</v>
@@ -3361,28 +3397,29 @@
       <c r="I18" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
@@ -3390,28 +3427,29 @@
       <c r="I19" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" ht="76" customHeight="1" spans="1:9">
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" ht="76" customHeight="1" spans="1:10">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>14</v>
@@ -3419,28 +3457,29 @@
       <c r="I20" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>14</v>
@@ -3448,28 +3487,29 @@
       <c r="I21" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" ht="76" customHeight="1" spans="1:9">
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" ht="76" customHeight="1" spans="1:10">
       <c r="A22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
@@ -3477,28 +3517,31 @@
       <c r="I22" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" ht="76" customHeight="1" spans="1:9">
+      <c r="J22" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1" spans="1:10">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -3506,28 +3549,29 @@
       <c r="I23" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" ht="76" customHeight="1" spans="1:9">
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" ht="76" customHeight="1" spans="1:10">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>14</v>
@@ -3535,28 +3579,31 @@
       <c r="I24" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J24" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>14</v>
@@ -3564,28 +3611,29 @@
       <c r="I25" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" ht="76" customHeight="1" spans="1:9">
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" ht="76" customHeight="1" spans="1:10">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>14</v>
@@ -3593,28 +3641,31 @@
       <c r="I26" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J26" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A27" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
@@ -3622,28 +3673,29 @@
       <c r="I27" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" ht="76" customHeight="1" spans="1:9">
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" ht="76" customHeight="1" spans="1:10">
       <c r="A28" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>14</v>
@@ -3651,28 +3703,31 @@
       <c r="I28" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J28" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A29" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
@@ -3680,28 +3735,29 @@
       <c r="I29" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A30" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>14</v>
@@ -3709,28 +3765,29 @@
       <c r="I30" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" ht="76" customHeight="1" spans="1:9">
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" ht="76" customHeight="1" spans="1:10">
       <c r="A31" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>14</v>
@@ -3738,28 +3795,31 @@
       <c r="I31" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J31" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A32" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>14</v>
@@ -3767,28 +3827,29 @@
       <c r="I32" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" ht="76" hidden="1" customHeight="1" spans="1:9">
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" ht="76" hidden="1" customHeight="1" spans="1:10">
       <c r="A33" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
@@ -3796,63 +3857,70 @@
       <c r="I33" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" ht="76" customHeight="1" spans="1:9">
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" ht="76" customHeight="1" spans="1:10">
       <c r="A34" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" ht="76" customHeight="1" spans="1:9">
+        <v>211</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" ht="76" customHeight="1" spans="1:10">
       <c r="A35" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3886,20 +3954,20 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6">
       <c r="A3" s="16" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="62" customHeight="1" spans="1:6">
       <c r="A4" s="17" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -3911,7 +3979,7 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -3920,10 +3988,10 @@
     </row>
     <row r="6" ht="62" customHeight="1" spans="1:6">
       <c r="A6" s="17" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -3932,10 +4000,10 @@
     </row>
     <row r="7" ht="62" customHeight="1" spans="1:6">
       <c r="A7" s="17" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -3947,7 +4015,7 @@
         <v>76</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -3956,10 +4024,10 @@
     </row>
     <row r="9" ht="62" customHeight="1" spans="1:6">
       <c r="A9" s="17" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -3968,15 +4036,15 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6">
       <c r="A11" s="16" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" ht="62" customHeight="1" spans="1:6">
       <c r="A12" s="17" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -3988,7 +4056,7 @@
         <v>75</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -3997,10 +4065,10 @@
     </row>
     <row r="14" ht="62" customHeight="1" spans="1:6">
       <c r="A14" s="17" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -4009,10 +4077,10 @@
     </row>
     <row r="15" ht="62" customHeight="1" spans="1:6">
       <c r="A15" s="17" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -4024,7 +4092,7 @@
         <v>76</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -4033,10 +4101,10 @@
     </row>
     <row r="17" ht="62" customHeight="1" spans="1:6">
       <c r="A17" s="17" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -4084,784 +4152,784 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>235</v>
-      </c>
       <c r="H6" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="G20" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>14</v>
@@ -4869,36 +4937,36 @@
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="12" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C35" s="13">
         <v>30</v>
@@ -4907,7 +4975,7 @@
     <row r="36" spans="1:8">
       <c r="A36" s="14"/>
       <c r="B36" s="14" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C36" s="14">
         <v>17</v>
@@ -4916,7 +4984,7 @@
     <row r="37" spans="1:8">
       <c r="A37" s="14"/>
       <c r="B37" s="14" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C37" s="14">
         <v>8</v>
@@ -4925,7 +4993,7 @@
     <row r="38" spans="1:8">
       <c r="A38" s="14"/>
       <c r="B38" s="14" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C38" s="14">
         <v>2</v>
@@ -4934,7 +5002,7 @@
     <row r="39" spans="1:8">
       <c r="A39" s="14"/>
       <c r="B39" s="14" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C39" s="14">
         <v>1</v>
@@ -4943,7 +5011,7 @@
     <row r="40" spans="1:8">
       <c r="A40" s="14"/>
       <c r="B40" s="14" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C40" s="14">
         <v>2</v>
@@ -4952,7 +5020,7 @@
     <row r="41" spans="1:8">
       <c r="A41" s="14"/>
       <c r="B41" s="14" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C41" s="15">
         <v>0.633333333333333</v>
